--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ДИРЕКЦИЯ КУЛТУРА/ОБЩИНА ВАРНА % 5 - ДИРЕКЦИЯ КУЛТУРА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ДИРЕКЦИЯ КУЛТУРА/ОБЩИНА ВАРНА % 5 - ДИРЕКЦИЯ КУЛТУРА.xlsx
@@ -104,7 +104,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="8">
-        <v>1.65</v>
+        <v>1.649963</v>
       </c>
       <c r="E7" s="7">
         <v>89.56</v>
